--- a/04_DESIGN_TABLES/DesignTable_2602_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2602_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL6"/>
+  <dimension ref="A1:BL7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1369,32 +1369,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2602-12-12-12-FG</t>
+          <t>2602-08-08-08-FG</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="C5" t="n">
-        <v>0.655</v>
+        <v>0.531</v>
       </c>
       <c r="D5" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="E5" t="n">
-        <v>0.125</v>
+        <v>0.094</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3895</v>
+        <v>0.2837</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4715</v>
+        <v>0.3295</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1299</v>
+        <v>0.0984</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
@@ -1403,28 +1403,28 @@
         <v>37</v>
       </c>
       <c r="L5" t="n">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="M5" t="n">
-        <v>0.655</v>
+        <v>0.531</v>
       </c>
       <c r="N5" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="O5" t="n">
-        <v>0.125</v>
+        <v>0.094</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3895</v>
+        <v>0.2837</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4715</v>
+        <v>0.3295</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1299</v>
+        <v>0.0984</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="T5" t="n">
         <v>60</v>
@@ -1433,112 +1433,112 @@
         <v>37</v>
       </c>
       <c r="V5" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="W5" t="n">
-        <v>0.655</v>
+        <v>0.531</v>
       </c>
       <c r="X5" t="n">
-        <v>0.61</v>
+        <v>0.391</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.61</v>
+        <v>0.391</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.61</v>
+        <v>0.391</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.0625</v>
+        <v>0.75</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.3895</v>
+        <v>0.2837</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.04511</v>
+        <v>0.03383</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.02083</v>
+        <v>0.01562</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.0625</v>
+        <v>0.75</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.3895</v>
+        <v>0.2837</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.04511</v>
+        <v>0.03383</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.02083</v>
+        <v>0.01562</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="AT5" t="n">
         <v>0.07142999999999999</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.455</v>
+        <v>0.35</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.51214</v>
+        <v>0.40714</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.31</v>
+        <v>1.062</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.026</v>
+        <v>0.863</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.026</v>
+        <v>0.863</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.31</v>
+        <v>1.062</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>2602-12-12-12-FG</t>
+          <t>2602-08-08-08-FG</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>Female Branch Tee, 1 1/16-12 JIC x 1 1/16-12 JIC x 3/4-14 NPTF (female)</t>
+          <t>Female Branch Tee, 3/4-16 JIC x 3/4-16 JIC x 1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -1548,64 +1548,69 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1 1/16-12 JIC</t>
+          <t>3/4-16 JIC</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>1 1/16-12 JIC</t>
+          <t>3/4-16 JIC</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>Air-Way s171 (double-pass 20 rows; survey said 21 - page wins); pipe-end M1/N1/Y1 == MS51506F Amd1 on matched FG combos; JIC ends VERIFIED (MS33656J) | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D1 column (ASSUMPTION); each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2602-08-08-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): M1_1@DRIVE: Brennan TFA catalog p.49 table TFA-p049-t02 "2602-FG MJ-MJ-FP TEE" row 2602-08-08-08-FG col "M1 LGTH" = "1.520" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 418.9, page verified True) [Brennan = yes 2026-10-18] - B1 JIC run leg (column mapping: REPORT.md, table 2602); = OMi WebsitePartsInfo2026 Items!N815 "M 1 Size" = 1.520 (same value; OMi and Brennan count as one source); M1_2@DRIVE: Brennan TFA catalog p.49 table TFA-p049-t02 "2602-FG MJ-MJ-FP TEE" row 2602-08-08-08-FG col "M2 LGTH" = "1.520" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 418.9, page verified True) [Brennan = yes 2026-10-18] - B2 JIC run leg (column mapping: REPORT.md, table 2602); = OMi WebsitePartsInfo2026 Items!O815 "M 2 Size" = 1.520 (same value; OMi and Brennan count as one source); N1@DRIVE: Brennan TFA catalog p.49 table TFA-p049-t02 "2602-FG MJ-MJ-FP TEE" row 2602-08-08-08-FG col "N LGTH" = "1.230" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 418.9, page verified True) [Brennan = yes 2026-10-18] - run axis to the female NPTF branch port face (column mapping: REPORT.md, table 2602); = OMi WebsitePartsInfo2026 Items!P815 "L 1 Size" = 1.230 (same value; OMi and Brennan count as one source); Y1@DRIVE: Brennan TFA catalog p.49 table TFA-p049-t02 "2602-FG MJ-MJ-FP TEE" row 2602-08-08-08-FG col "Y FLATS" = "1.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 418.9, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 2602); = OMi WebsitePartsInfo2026 Items!R815 "Hex Flat" = 1.062 (same value; OMi and Brennan count as one source); D1@BORE: Brennan TFA catalog p.49 table TFA-p049-t02 "2602-FG MJ-MJ-FP TEE" row 2602-08-08-08-FG col "B1 DRILL" = "0.391" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 418.9, page verified True) [Brennan = yes 2026-10-18] - B1 JIC drill (column mapping: REPORT.md, table 2602); = OMi WebsitePartsInfo2026 Items!S815 "Side 1 ID" = 0.391 (same value; OMi and Brennan count as one source); D2@BORE: Brennan TFA catalog p.49 table TFA-p049-t02 "2602-FG MJ-MJ-FP TEE" row 2602-08-08-08-FG col "B2 DRILL" = "0.391" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 418.9, page verified True) [Brennan = yes 2026-10-18] - B2 JIC drill (column mapping: REPORT.md, table 2602); = OMi WebsitePartsInfo2026 Items!X815 "Side 2 ID" = 0.391 (same value; OMi and Brennan count as one source); TAPDRILL@BORE: end library: tap drill of the -08 female NPTF port = 0.7 (gen_straight2 FPT[8] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-TRANSFER-TAPDRILL = A1 answered YES 2026-10-18 (00_DOCS/ANSWERS_2026-10-18.md): Air-Way per-size tap drill on existing families]; THDMAJ_B1@DRIVE: end library: male JIC -08 thread major = 0.75 (gen_straight2 JIC[8] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_B2@DRIVE: end library: male JIC -08 thread major = 0.75 (gen_straight2 JIC[8] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A@DRIVE: end library: pipe OD of the -08 NPTF thread = 0.84 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[8], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p049-t02 thread columns (B1 SAE 37Deg 3/4-16, B2 SAE 37Deg 3/4-16, A3 NPTF 1/2-14) and OMi Items Side 1 / 2 / 3 Thread | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D1 column (ASSUMPTION); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2602-08-08-08 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog (= OMi Items, one source), end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>2602-12-12-12-FG</t>
+          <t>2602-08-08-08-FG</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2602-16-16-16-FG</t>
+          <t>2602-12-12-12-FG</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.17</v>
+        <v>1.89</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.655</v>
       </c>
       <c r="D6" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="E6" t="n">
         <v>0.125</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5965</v>
+        <v>0.4715</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1292</v>
+        <v>0.1299</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1858</v>
+        <v>0.1851</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
@@ -1614,28 +1619,28 @@
         <v>37</v>
       </c>
       <c r="L6" t="n">
-        <v>2.17</v>
+        <v>1.89</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.655</v>
       </c>
       <c r="N6" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="O6" t="n">
         <v>0.125</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5965</v>
+        <v>0.4715</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1292</v>
+        <v>0.1299</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1858</v>
+        <v>0.1851</v>
       </c>
       <c r="T6" t="n">
         <v>60</v>
@@ -1644,43 +1649,43 @@
         <v>37</v>
       </c>
       <c r="V6" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.655</v>
       </c>
       <c r="X6" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.17</v>
+        <v>1.89</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.17</v>
+        <v>1.89</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="AG6" t="n">
         <v>0.08333</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="AI6" t="n">
         <v>0.04511</v>
@@ -1692,13 +1697,13 @@
         <v>0.08333</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="AM6" t="n">
         <v>0.08333</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="AO6" t="n">
         <v>0.04511</v>
@@ -1710,79 +1715,290 @@
         <v>0.08333</v>
       </c>
       <c r="AR6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.51214</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.026</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.026</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>2602-12-12-12-FG</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>Female Branch Tee, 1 1/16-12 JIC x 1 1/16-12 JIC x 3/4-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>2602</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>1 1/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>1 1/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>Air-Way s171 (double-pass 20 rows; survey said 21 - page wins); pipe-end M1/N1/Y1 == MS51506F Amd1 on matched FG combos; JIC ends VERIFIED (MS33656J) | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D1 column (ASSUMPTION); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>2602-12-12-12-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2602-16-16-16-FG</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="J7" t="n">
+        <v>60</v>
+      </c>
+      <c r="K7" t="n">
+        <v>37</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="T7" t="n">
+        <v>60</v>
+      </c>
+      <c r="U7" t="n">
+        <v>37</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1.14</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="AC7" t="n">
         <v>1.14</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="AD7" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AT7" t="n">
         <v>0.08696</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="AU7" t="n">
         <v>0.57</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AV7" t="n">
         <v>0.63957</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="AW7" t="n">
         <v>1.62</v>
       </c>
-      <c r="AX6" t="n">
+      <c r="AX7" t="n">
         <v>1.63</v>
       </c>
-      <c r="AY6" t="n">
+      <c r="AY7" t="n">
         <v>1.259</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="AZ7" t="n">
         <v>1.259</v>
       </c>
-      <c r="BA6" t="n">
+      <c r="BA7" t="n">
         <v>1.63</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="BB7" t="n">
         <v>1.36</v>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>2602-16-16-16-FG</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BD7" t="inlineStr">
         <is>
           <t>Female Branch Tee, 1 5/16-12 JIC x 1 5/16-12 JIC x 1-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>2602</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>1 5/16-12 JIC</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>1 5/16-12 JIC</t>
         </is>
       </c>
-      <c r="BH6" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>1-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>Air-Way s171 (double-pass 20 rows; survey said 21 - page wins); pipe-end M1/N1/Y1 == MS51506F Amd1 on matched FG combos; JIC ends VERIFIED (MS33656J) | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D1 column (ASSUMPTION); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>2602-16-16-16-FG</t>
         </is>
